--- a/Python/dz2/work/output/animals_status_species.xlsx
+++ b/Python/dz2/work/output/animals_status_species.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="28">
   <si>
     <t>inventory_number</t>
   </si>
@@ -40,16 +40,61 @@
     <t>A-001</t>
   </si>
   <si>
+    <t>A-006</t>
+  </si>
+  <si>
+    <t>A-011</t>
+  </si>
+  <si>
+    <t>A-018</t>
+  </si>
+  <si>
+    <t>A-021</t>
+  </si>
+  <si>
+    <t>A-030</t>
+  </si>
+  <si>
+    <t>A-035</t>
+  </si>
+  <si>
     <t>Муся</t>
   </si>
   <si>
+    <t>Барсик</t>
+  </si>
+  <si>
+    <t>Нора</t>
+  </si>
+  <si>
+    <t>Рыжик</t>
+  </si>
+  <si>
+    <t>Мила</t>
+  </si>
+  <si>
+    <t>Снежок</t>
+  </si>
+  <si>
+    <t>Лея</t>
+  </si>
+  <si>
     <t>Кошка</t>
   </si>
   <si>
     <t>Персидская</t>
   </si>
   <si>
+    <t>Мейн-кун</t>
+  </si>
+  <si>
+    <t>Британская короткошерстная</t>
+  </si>
+  <si>
     <t>F</t>
+  </si>
+  <si>
+    <t>M</t>
   </si>
   <si>
     <t>В приюте</t>
@@ -410,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -441,22 +486,154 @@
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F2">
         <v>4</v>
       </c>
       <c r="G2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3">
+        <v>3.7</v>
+      </c>
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4">
+        <v>3.7</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5">
+        <v>2.3</v>
+      </c>
+      <c r="G5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6">
+        <v>2.5</v>
+      </c>
+      <c r="G6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
         <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7">
+        <v>2.4</v>
+      </c>
+      <c r="G7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8">
+        <v>2.9</v>
+      </c>
+      <c r="G8" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
